--- a/Logger/Korrelationstabelle_MTW.xlsx
+++ b/Logger/Korrelationstabelle_MTW.xlsx
@@ -1,29 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F894FD7-DFC1-40D8-ABC3-533268C79971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF995D-A361-443A-B081-1694B56B8E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$101</definedName>
-  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="14">
   <si>
     <t>MTW_var</t>
   </si>
@@ -56,6 +53,9 @@
   </si>
   <si>
     <t>MTO</t>
+  </si>
+  <si>
+    <t>MTW</t>
   </si>
   <si>
     <t>MTN</t>
@@ -126,9 +126,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -433,13 +435,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="1" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -456,7 +456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -470,7 +470,7 @@
         <v>0.88478866845068904</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -478,10 +478,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>0.88609535534178097</v>
+        <v>0.80369910334616002</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -489,30 +489,30 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3">
-        <v>0.81999651092439374</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.71374883016685164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3">
-        <v>0.95310154035599226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.46251860530097222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -526,7 +526,7 @@
         <v>0.64575517635531299</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -540,7 +540,7 @@
         <v>0.82373791372955951</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -548,10 +548,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3">
-        <v>0.87527996417078824</v>
+        <v>0.85959541399075923</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -559,30 +559,30 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0.80474778879645315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.6305557582858502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>0.94715391533186666</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.65335964168237304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -596,7 +596,7 @@
         <v>0.43761869077876753</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -610,18 +610,18 @@
         <v>-0.70787705055813721</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3">
-        <v>0.86294029166235209</v>
+        <v>-0.63183122360981203</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -632,27 +632,27 @@
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3">
-        <v>0.77728968356926642</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.77536888467174403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3">
-        <v>0.9444995296843729</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.15386457879305529</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
@@ -666,7 +666,7 @@
         <v>-0.45382477530962312</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -680,18 +680,18 @@
         <v>0.46275855626541418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>0.85959541399075923</v>
+        <v>0.72403408078447773</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -699,16 +699,16 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="3">
-        <v>0.77536888467174403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.199857142674811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -722,7 +722,7 @@
         <v>0.9136870109516867</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
@@ -736,7 +736,7 @@
         <v>0.14914080085092299</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
@@ -750,18 +750,18 @@
         <v>0.68907593118401889</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3">
-        <v>0.84135986317361322</v>
+        <v>0.51641786891722319</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -769,30 +769,30 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1769979206542536</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.58564535026855558</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D25" s="3">
-        <v>0.66715347056963881</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.1462666456689265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>9</v>
       </c>
@@ -806,7 +806,7 @@
         <v>0.67408690543250938</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
@@ -820,7 +820,7 @@
         <v>0.78104202855317928</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>6</v>
       </c>
@@ -828,10 +828,10 @@
         <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3">
-        <v>0.80369910334616002</v>
+        <v>0.7829287434769886</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -839,30 +839,30 @@
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="3">
-        <v>0.16467372280629861</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.57468074441146488</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3">
-        <v>0.65335964168237304</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.44425417970982811</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -876,7 +876,7 @@
         <v>0.43455301440597338</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
@@ -890,18 +890,18 @@
         <v>0.76113984260189904</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="3">
-        <v>0.80256565715379968</v>
+        <v>0.84135986317361322</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -909,16 +909,16 @@
         <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" s="3">
-        <v>0.10011222197633329</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.45513317643763512</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -932,7 +932,7 @@
         <v>0.63173125736033908</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>9</v>
       </c>
@@ -946,7 +946,7 @@
         <v>0.3186029511083075</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>4</v>
       </c>
@@ -960,18 +960,18 @@
         <v>-0.60699363499826586</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="3">
-        <v>0.7829287434769886</v>
+        <v>-0.42349181805270558</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -979,30 +979,30 @@
         <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3">
-        <v>-0.199857142674811</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.77728968356926642</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3">
-        <v>0.60242724745810716</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.17831539632163629</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>-0.39838382843572068</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>0.37076854171864337</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>6</v>
       </c>
@@ -1038,10 +1038,10 @@
         <v>8</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D43" s="3">
-        <v>0.72403408078447773</v>
+        <v>0.63477930656059867</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,30 +1049,30 @@
         <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="3">
-        <v>-0.45513317643763512</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.16467372280629861</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3">
-        <v>0.55395220552469426</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.94715391533186666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>9.1677791881930436E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>4</v>
       </c>
@@ -1100,18 +1100,18 @@
         <v>0.56684542292129736</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="3">
-        <v>0.68250068244057349</v>
+        <v>0.44494276045185432</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,30 +1119,30 @@
         <v>7</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3">
-        <v>-0.46189208819676081</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.53936996493490996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3">
-        <v>0.46251860530097222</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>5.0778553395172198E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>9</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>0.47871324519773689</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
@@ -1167,21 +1167,21 @@
         <v>11</v>
       </c>
       <c r="D52" s="3">
-        <v>0.8891546903898857</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" s="3">
-        <v>0.63477930656059867</v>
+        <v>0.84731748511254823</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1189,16 +1189,16 @@
         <v>7</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3">
-        <v>-0.50917250501690403</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.68817336711292454</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>8</v>
       </c>
@@ -1206,13 +1206,13 @@
         <v>4</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="3">
-        <v>0.44425417970982811</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.40733545535555171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>9</v>
       </c>
@@ -1223,10 +1223,10 @@
         <v>11</v>
       </c>
       <c r="D56" s="3">
-        <v>0.65630160864197262</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.8085462947706854</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>4</v>
       </c>
@@ -1237,21 +1237,21 @@
         <v>11</v>
       </c>
       <c r="D57" s="3">
-        <v>0.81181498728881807</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.84731748511254823</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D58" s="3">
-        <v>0.6288634912359139</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1259,30 +1259,30 @@
         <v>7</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59" s="3">
-        <v>-0.53936996493490996</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.60969434265037359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="3">
-        <v>0.37730889837655551</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.68107545134074554</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>9</v>
       </c>
@@ -1293,10 +1293,10 @@
         <v>11</v>
       </c>
       <c r="D61" s="3">
-        <v>0.40101283105084351</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.49190100523110752</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>4</v>
       </c>
@@ -1307,21 +1307,21 @@
         <v>11</v>
       </c>
       <c r="D62" s="3">
-        <v>-0.6151136246093668</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.68817336711292454</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D63" s="3">
-        <v>0.51641786891722319</v>
+        <v>-0.60969434265037359</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1329,16 +1329,16 @@
         <v>7</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D64" s="3">
-        <v>-0.54022634440067008</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
@@ -1346,13 +1346,13 @@
         <v>7</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="3">
-        <v>0.23515638517454679</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.15505288118667199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>9</v>
       </c>
@@ -1363,10 +1363,10 @@
         <v>11</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.43317103542797969</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.61446808830061461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>4</v>
       </c>
@@ -1377,21 +1377,21 @@
         <v>11</v>
       </c>
       <c r="D67" s="3">
-        <v>0.45551868227170672</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.40733545535555171</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D68" s="3">
-        <v>0.51056616390088572</v>
+        <v>0.68107545134074554</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,30 +1399,30 @@
         <v>7</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D69" s="3">
-        <v>-0.57468074441146488</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.15505288118667199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="3">
-        <v>0.21345554943034559</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>9</v>
       </c>
@@ -1433,10 +1433,10 @@
         <v>11</v>
       </c>
       <c r="D71" s="3">
-        <v>8.9063365304479045E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>2.210961404066094E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>4</v>
       </c>
@@ -1447,10 +1447,10 @@
         <v>11</v>
       </c>
       <c r="D72" s="3">
-        <v>0.70637683042315225</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.8085462947706854</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -1458,10 +1458,10 @@
         <v>9</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" s="3">
-        <v>0.45064282546361523</v>
+        <v>0.49190100523110752</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1472,27 +1472,27 @@
         <v>9</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D74" s="3">
-        <v>-0.58564535026855558</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.61446808830061461</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" s="3">
-        <v>0.17831539632163629</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>2.210961404066094E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>9</v>
       </c>
@@ -1503,10 +1503,10 @@
         <v>11</v>
       </c>
       <c r="D76" s="3">
-        <v>0.72712821190621657</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>4</v>
       </c>
@@ -1517,21 +1517,21 @@
         <v>12</v>
       </c>
       <c r="D77" s="3">
-        <v>0.88954122212209208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.8891546903898857</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D78" s="3">
-        <v>0.44494276045185432</v>
+        <v>0.80256565715379968</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,24 +1545,24 @@
         <v>12</v>
       </c>
       <c r="D79" s="3">
-        <v>-0.59684432334287452</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.65725846827891898</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D80" s="3">
-        <v>0.1462666456689265</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.37730889837655551</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
@@ -1573,10 +1573,10 @@
         <v>12</v>
       </c>
       <c r="D81" s="3">
-        <v>0.554974663564204</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.65630160864197262</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>4</v>
       </c>
@@ -1587,21 +1587,21 @@
         <v>12</v>
       </c>
       <c r="D82" s="3">
-        <v>0.79238208755251849</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.81181498728881807</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="3">
-        <v>-0.41155227220434121</v>
+        <v>0.86294029166235209</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1609,30 +1609,30 @@
         <v>7</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D84" s="3">
-        <v>-0.62522262694071218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.50917250501690403</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="3">
-        <v>5.9780040388593317E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.60242724745810716</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>9</v>
       </c>
@@ -1643,10 +1643,10 @@
         <v>12</v>
       </c>
       <c r="D86" s="3">
-        <v>0.35411537251932701</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.40101283105084351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>4</v>
       </c>
@@ -1657,10 +1657,10 @@
         <v>12</v>
       </c>
       <c r="D87" s="3">
-        <v>-0.62131799149465328</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.6151136246093668</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>6</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>7</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" s="3">
         <v>-0.41829837085207661</v>
@@ -1679,30 +1679,30 @@
         <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D89" s="3">
-        <v>-0.6305557582858502</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.80474778879645315</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D90" s="3">
-        <v>5.0778553395172198E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.21345554943034559</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>9</v>
       </c>
@@ -1713,10 +1713,10 @@
         <v>12</v>
       </c>
       <c r="D91" s="3">
-        <v>-0.4364231608772457</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.43317103542797969</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>4</v>
       </c>
@@ -1727,21 +1727,21 @@
         <v>12</v>
       </c>
       <c r="D92" s="3">
-        <v>0.35831134095937761</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.45551868227170672</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D93" s="3">
-        <v>-0.42349181805270558</v>
+        <v>0.68250068244057349</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -1749,30 +1749,30 @@
         <v>7</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D94" s="3">
-        <v>-0.65725846827891898</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.10011222197633329</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D95" s="3">
-        <v>3.4154132245768E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.9444995296843729</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>9</v>
       </c>
@@ -1783,10 +1783,10 @@
         <v>12</v>
       </c>
       <c r="D96" s="3">
-        <v>4.9897736095897809E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>8.9063365304479045E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>4</v>
       </c>
@@ -1797,21 +1797,21 @@
         <v>12</v>
       </c>
       <c r="D97" s="3">
-        <v>0.61282960481434001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.70637683042315225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D98" s="3">
-        <v>-0.63183122360981203</v>
+        <v>0.51056616390088572</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -1819,30 +1819,30 @@
         <v>7</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D99" s="3">
-        <v>-0.71374883016685164</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>-0.62522262694071218</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D100" s="3">
-        <v>-0.15386457879305529</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>3.4154132245768E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>9</v>
       </c>
@@ -1853,20 +1853,360 @@
         <v>12</v>
       </c>
       <c r="D101" s="3">
+        <v>0.72712821190621657</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0.88954122212209208</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="3">
+        <v>0.88609535534178097</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="3">
+        <v>-0.59684432334287452</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="3">
+        <v>0.55395220552469426</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0.554974663564204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="3">
+        <v>0.79238208755251849</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="3">
+        <v>0.87527996417078824</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="3">
+        <v>-0.46189208819676081</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="3">
+        <v>0.66715347056963881</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="3">
+        <v>0.35411537251932701</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="3">
+        <v>-0.62131799149465328</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="3">
+        <v>-0.41155227220434121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="3">
+        <v>0.81999651092439374</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="3">
+        <v>0.23515638517454679</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="3">
+        <v>-0.4364231608772457</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="3">
+        <v>0.35831134095937761</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="3">
+        <v>0.6288634912359139</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="3">
+        <v>0.1769979206542536</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="3">
+        <v>0.95310154035599226</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="3">
+        <v>4.9897736095897809E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="3">
+        <v>0.61282960481434001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="3">
+        <v>0.45064282546361523</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="3">
+        <v>-0.54022634440067008</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="3">
+        <v>5.9780040388593317E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="3">
         <v>0.64187674131062356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D101" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="relLF_percent"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:D99">
-      <sortCondition descending="1" ref="D1:D101"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Logger/Korrelationstabelle_MTW.xlsx
+++ b/Logger/Korrelationstabelle_MTW.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF995D-A361-443A-B081-1694B56B8E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEC23A3-3DAA-497C-9F2C-71895968F2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$126</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -435,6 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -456,7 +460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -464,10 +468,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>0.88478866845068904</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -475,30 +479,30 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>0.80369910334616002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3">
-        <v>-0.71374883016685164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -512,32 +516,32 @@
         <v>0.46251860530097222</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3">
-        <v>0.64575517635531299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3">
-        <v>0.82373791372955951</v>
+        <v>0.88954122212209208</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -545,30 +549,30 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3">
-        <v>0.85959541399075923</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.88609535534178097</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D9" s="3">
-        <v>-0.6305557582858502</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.81999651092439374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -582,32 +586,32 @@
         <v>0.65335964168237304</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3">
-        <v>0.43761869077876753</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.8085462947706854</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3">
-        <v>-0.70787705055813721</v>
+        <v>0.8891546903898857</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -615,16 +619,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D13" s="3">
-        <v>-0.63183122360981203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.87527996417078824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
@@ -632,13 +636,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3">
-        <v>0.77536888467174403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.80474778879645315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
@@ -652,32 +656,32 @@
         <v>-0.15386457879305529</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3">
-        <v>-0.45382477530962312</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.72712821190621657</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="3">
-        <v>0.46275855626541418</v>
+        <v>0.88478866845068904</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -685,30 +689,30 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>0.72403408078447773</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.86294029166235209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" s="3">
-        <v>-0.199857142674811</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.77728968356926642</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -722,32 +726,32 @@
         <v>0.9136870109516867</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="3">
-        <v>0.14914080085092299</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.67408690543250938</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D22" s="3">
-        <v>0.68907593118401889</v>
+        <v>0.84731748511254823</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -755,30 +759,30 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="3">
-        <v>0.51641786891722319</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.85959541399075923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="3">
-        <v>-0.58564535026855558</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.77536888467174403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -792,32 +796,32 @@
         <v>0.1462666456689265</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="3">
-        <v>0.67408690543250938</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.65630160864197262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D27" s="3">
-        <v>0.78104202855317928</v>
+        <v>0.82373791372955951</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -828,27 +832,27 @@
         <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="3">
-        <v>0.7829287434769886</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.84731748511254823</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D29" s="3">
-        <v>-0.57468074441146488</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.1769979206542536</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -862,7 +866,7 @@
         <v>0.44425417970982811</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -870,13 +874,13 @@
         <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3">
-        <v>0.43455301440597338</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.64575517635531299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
@@ -884,10 +888,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3">
-        <v>0.76113984260189904</v>
+        <v>0.81181498728881807</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -904,21 +908,21 @@
         <v>0.84135986317361322</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="3">
-        <v>-0.45513317643763512</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.16467372280629861</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -932,32 +936,32 @@
         <v>0.63173125736033908</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D36" s="3">
-        <v>0.3186029511083075</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.64187674131062356</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" s="3">
-        <v>-0.60699363499826586</v>
+        <v>0.8085462947706854</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -965,30 +969,30 @@
         <v>6</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>-0.42349181805270558</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.80369910334616002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="3">
-        <v>0.77728968356926642</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.15505288118667199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
@@ -1002,32 +1006,32 @@
         <v>0.17831539632163629</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D41" s="3">
-        <v>-0.39838382843572068</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.554974663564204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D42" s="3">
-        <v>0.37076854171864337</v>
+        <v>0.79238208755251849</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,16 +1039,16 @@
         <v>6</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D43" s="3">
-        <v>0.63477930656059867</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.80256565715379968</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>7</v>
       </c>
@@ -1052,13 +1056,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D44" s="3">
-        <v>0.16467372280629861</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.10011222197633329</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
@@ -1072,32 +1076,32 @@
         <v>0.94715391533186666</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" s="3">
-        <v>9.1677791881930436E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.49190100523110752</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="3">
-        <v>0.56684542292129736</v>
+        <v>0.78104202855317928</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,30 +1109,30 @@
         <v>6</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="3">
-        <v>0.44494276045185432</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.7829287434769886</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D49" s="3">
-        <v>-0.53936996493490996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.199857142674811</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>8</v>
       </c>
@@ -1142,7 +1146,7 @@
         <v>5.0778553395172198E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>9</v>
       </c>
@@ -1156,18 +1160,18 @@
         <v>0.47871324519773689</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D52" s="3">
-        <v>0.99999999999999989</v>
+        <v>0.76113984260189904</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1175,30 +1179,30 @@
         <v>6</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D53" s="3">
-        <v>0.84731748511254823</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.72403408078447773</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D54" s="3">
-        <v>-0.68817336711292454</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.45513317643763512</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>8</v>
       </c>
@@ -1212,32 +1216,32 @@
         <v>0.40733545535555171</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D56" s="3">
-        <v>0.8085462947706854</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.43761869077876753</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" s="3">
-        <v>0.84731748511254823</v>
+        <v>0.70637683042315225</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1245,16 +1249,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.68250068244057349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>7</v>
       </c>
@@ -1262,13 +1266,13 @@
         <v>6</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D59" s="3">
-        <v>-0.60969434265037359</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.46189208819676081</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
@@ -1282,32 +1286,32 @@
         <v>0.68107545134074554</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D61" s="3">
-        <v>0.49190100523110752</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.43455301440597338</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D62" s="3">
-        <v>-0.68817336711292454</v>
+        <v>0.68907593118401889</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,30 +1319,30 @@
         <v>6</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="3">
-        <v>-0.60969434265037359</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.68107545134074554</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D64" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.50917250501690403</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
@@ -1352,32 +1356,32 @@
         <v>0.15505288118667199</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.61446808830061461</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.40101283105084351</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D67" s="3">
-        <v>0.40733545535555171</v>
+        <v>0.61282960481434001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,27 +1392,27 @@
         <v>8</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D68" s="3">
-        <v>0.68107545134074554</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.63477930656059867</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D69" s="3">
-        <v>0.15505288118667199</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.53936996493490996</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
@@ -1422,21 +1426,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D71" s="3">
-        <v>2.210961404066094E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.35411537251932701</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>4</v>
       </c>
@@ -1444,10 +1448,10 @@
         <v>9</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D72" s="3">
-        <v>0.8085462947706854</v>
+        <v>0.56684542292129736</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,16 +1459,16 @@
         <v>6</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D73" s="3">
-        <v>0.49190100523110752</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.6288634912359139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>7</v>
       </c>
@@ -1472,13 +1476,13 @@
         <v>9</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D74" s="3">
-        <v>-0.61446808830061461</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.54022634440067008</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
@@ -1492,32 +1496,32 @@
         <v>2.210961404066094E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D76" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.3186029511083075</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D77" s="3">
-        <v>0.8891546903898857</v>
+        <v>0.46275855626541418</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,16 +1529,16 @@
         <v>6</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D78" s="3">
-        <v>0.80256565715379968</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.51641786891722319</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
@@ -1542,13 +1546,13 @@
         <v>4</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D79" s="3">
-        <v>-0.65725846827891898</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.57468074441146488</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
@@ -1562,32 +1566,32 @@
         <v>0.37730889837655551</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D81" s="3">
-        <v>0.65630160864197262</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.14914080085092299</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="3">
-        <v>0.81181498728881807</v>
+        <v>0.45551868227170672</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1595,30 +1599,30 @@
         <v>6</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="3">
-        <v>0.86294029166235209</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.51056616390088572</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D84" s="3">
-        <v>-0.50917250501690403</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.58564535026855558</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>8</v>
       </c>
@@ -1632,32 +1636,32 @@
         <v>0.60242724745810716</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="3">
-        <v>0.40101283105084351</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8.9063365304479045E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D87" s="3">
-        <v>-0.6151136246093668</v>
+        <v>0.40733545535555171</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1665,30 +1669,30 @@
         <v>6</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D88" s="3">
-        <v>-0.41829837085207661</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.49190100523110752</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" s="3">
-        <v>0.80474778879645315</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.59684432334287452</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>8</v>
       </c>
@@ -1702,21 +1706,21 @@
         <v>0.21345554943034559</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" s="3">
-        <v>-0.43317103542797969</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2.210961404066094E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>4</v>
       </c>
@@ -1724,10 +1728,10 @@
         <v>8</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D92" s="3">
-        <v>0.45551868227170672</v>
+        <v>0.37076854171864337</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,30 +1739,30 @@
         <v>6</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D93" s="3">
-        <v>0.68250068244057349</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.45064282546361523</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" s="3">
-        <v>0.10011222197633329</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.60969434265037359</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>8</v>
       </c>
@@ -1772,7 +1776,7 @@
         <v>0.9444995296843729</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>9</v>
       </c>
@@ -1780,24 +1784,24 @@
         <v>8</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D96" s="3">
-        <v>8.9063365304479045E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9.1677791881930436E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D97" s="3">
-        <v>0.70637683042315225</v>
+        <v>0.35831134095937761</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,13 +1812,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D98" s="3">
-        <v>0.51056616390088572</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.44494276045185432</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>7</v>
       </c>
@@ -1822,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D99" s="3">
-        <v>-0.62522262694071218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.61446808830061461</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>8</v>
       </c>
@@ -1842,32 +1846,32 @@
         <v>3.4154132245768E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D101" s="3">
-        <v>0.72712821190621657</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.9897736095897809E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D102" s="3">
-        <v>0.88954122212209208</v>
+        <v>-0.60699363499826586</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,30 +1879,30 @@
         <v>6</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D103" s="3">
-        <v>0.88609535534178097</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.41155227220434121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" s="3">
-        <v>-0.59684432334287452</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.62522262694071218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>8</v>
       </c>
@@ -1912,32 +1916,32 @@
         <v>0.55395220552469426</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D106" s="3">
-        <v>0.554974663564204</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.39838382843572068</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D107" s="3">
-        <v>0.79238208755251849</v>
+        <v>-0.6151136246093668</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -1945,16 +1949,16 @@
         <v>6</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D108" s="3">
-        <v>0.87527996417078824</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.41829837085207661</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>7</v>
       </c>
@@ -1962,13 +1966,13 @@
         <v>6</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D109" s="3">
-        <v>-0.46189208819676081</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.6305557582858502</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>8</v>
       </c>
@@ -1982,21 +1986,21 @@
         <v>0.66715347056963881</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D111" s="3">
-        <v>0.35411537251932701</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.43317103542797969</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,27 +2022,27 @@
         <v>7</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D113" s="3">
-        <v>-0.41155227220434121</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.42349181805270558</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D114" s="3">
-        <v>0.81999651092439374</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.65725846827891898</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>8</v>
       </c>
@@ -2052,7 +2056,7 @@
         <v>0.23515638517454679</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>9</v>
       </c>
@@ -2066,18 +2070,18 @@
         <v>-0.4364231608772457</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D117" s="3">
-        <v>0.35831134095937761</v>
+        <v>-0.68817336711292454</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -2085,30 +2089,30 @@
         <v>6</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D118" s="3">
-        <v>0.6288634912359139</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.60969434265037359</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" s="3">
-        <v>0.1769979206542536</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.68817336711292454</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>8</v>
       </c>
@@ -2122,32 +2126,32 @@
         <v>0.95310154035599226</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D121" s="3">
-        <v>4.9897736095897809E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.45382477530962312</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D122" s="3">
-        <v>0.61282960481434001</v>
+        <v>-0.70787705055813721</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -2155,30 +2159,30 @@
         <v>6</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D123" s="3">
-        <v>0.45064282546361523</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.63183122360981203</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D124" s="3">
-        <v>-0.54022634440067008</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.71374883016685164</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>8</v>
       </c>
@@ -2192,21 +2196,31 @@
         <v>5.9780040388593317E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D126" s="3">
-        <v>0.64187674131062356</v>
+        <v>-0.61446808830061461</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Temp_schatten_C"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D123">
+      <sortCondition descending="1" ref="D1:D126"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Logger/Korrelationstabelle_MTW.xlsx
+++ b/Logger/Korrelationstabelle_MTW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEC23A3-3DAA-497C-9F2C-71895968F2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75AD002-335D-4DF0-8897-786837FB037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,13 +507,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>0.46251860530097222</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -577,13 +577,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3">
-        <v>0.65335964168237304</v>
+        <v>0.95310154035599226</v>
       </c>
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -647,13 +647,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>-0.15386457879305529</v>
+        <v>0.94715391533186666</v>
       </c>
     </row>
     <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="3">
-        <v>0.9136870109516867</v>
+        <v>0.9444995296843729</v>
       </c>
     </row>
     <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -787,13 +787,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1462666456689265</v>
+        <v>0.9136870109516867</v>
       </c>
     </row>
     <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -857,13 +857,13 @@
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="3">
-        <v>0.44425417970982811</v>
+        <v>0.68107545134074554</v>
       </c>
     </row>
     <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -930,10 +930,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D35" s="3">
-        <v>0.63173125736033908</v>
+        <v>0.66715347056963881</v>
       </c>
     </row>
     <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -997,13 +997,13 @@
         <v>8</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>0.17831539632163629</v>
+        <v>0.65335964168237304</v>
       </c>
     </row>
     <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1067,13 +1067,13 @@
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="3">
-        <v>0.94715391533186666</v>
+        <v>0.63173125736033908</v>
       </c>
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1137,13 +1137,13 @@
         <v>8</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D50" s="3">
-        <v>5.0778553395172198E-2</v>
+        <v>0.60242724745810716</v>
       </c>
     </row>
     <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1210,10 +1210,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D55" s="3">
-        <v>0.40733545535555171</v>
+        <v>0.55395220552469426</v>
       </c>
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1277,13 +1277,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D60" s="3">
-        <v>0.68107545134074554</v>
+        <v>0.46251860530097222</v>
       </c>
     </row>
     <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1347,13 +1347,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D65" s="3">
-        <v>0.15505288118667199</v>
+        <v>0.44425417970982811</v>
       </c>
     </row>
     <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1417,13 +1417,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="3">
-        <v>1</v>
+        <v>0.40733545535555171</v>
       </c>
     </row>
     <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1487,13 +1487,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75" s="3">
-        <v>2.210961404066094E-2</v>
+        <v>0.37730889837655551</v>
       </c>
     </row>
     <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1557,13 +1557,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D80" s="3">
-        <v>0.37730889837655551</v>
+        <v>0.23515638517454679</v>
       </c>
     </row>
     <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1627,13 +1627,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="3">
-        <v>0.60242724745810716</v>
+        <v>0.21345554943034559</v>
       </c>
     </row>
     <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1700,10 +1700,10 @@
         <v>7</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D90" s="3">
-        <v>0.21345554943034559</v>
+        <v>0.17831539632163629</v>
       </c>
     </row>
     <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1767,13 +1767,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D95" s="3">
-        <v>0.9444995296843729</v>
+        <v>0.15505288118667199</v>
       </c>
     </row>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1840,10 +1840,10 @@
         <v>9</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D100" s="3">
-        <v>3.4154132245768E-2</v>
+        <v>0.1462666456689265</v>
       </c>
     </row>
     <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1907,13 +1907,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D105" s="3">
-        <v>0.55395220552469426</v>
+        <v>5.9780040388593317E-2</v>
       </c>
     </row>
     <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1977,13 +1977,13 @@
         <v>8</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D110" s="3">
-        <v>0.66715347056963881</v>
+        <v>5.0778553395172198E-2</v>
       </c>
     </row>
     <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2047,13 +2047,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" s="3">
-        <v>0.23515638517454679</v>
+        <v>3.4154132245768E-2</v>
       </c>
     </row>
     <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2117,13 +2117,13 @@
         <v>8</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D120" s="3">
-        <v>0.95310154035599226</v>
+        <v>2.210961404066094E-2</v>
       </c>
     </row>
     <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2187,13 +2187,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D125" s="3">
-        <v>5.9780040388593317E-2</v>
+        <v>-0.15386457879305529</v>
       </c>
     </row>
     <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2217,7 +2217,7 @@
         <filter val="Temp_schatten_C"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D123">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D125">
       <sortCondition descending="1" ref="D1:D126"/>
     </sortState>
   </autoFilter>
